--- a/static/sample-data/synth_retail_ecom.xlsx
+++ b/static/sample-data/synth_retail_ecom.xlsx
@@ -437,19 +437,19 @@
         <v>44592</v>
       </c>
       <c r="B2">
-        <v>1267533939</v>
+        <v>1136444333</v>
       </c>
       <c r="C2">
-        <v>34959150</v>
+        <v>42649380</v>
       </c>
       <c r="D2">
-        <v>142.8</v>
+        <v>174.2</v>
       </c>
       <c r="E2">
-        <v>47162229</v>
+        <v>38537752</v>
       </c>
       <c r="F2">
-        <v>226128815</v>
+        <v>184777019</v>
       </c>
       <c r="G2">
         <v>7612938</v>
@@ -458,10 +458,10 @@
         <v>95521107</v>
       </c>
       <c r="I2">
-        <v>12428834</v>
+        <v>7768021</v>
       </c>
       <c r="J2">
-        <v>25486123</v>
+        <v>15928827</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -478,19 +478,19 @@
         <v>44620</v>
       </c>
       <c r="B3">
-        <v>1327952220</v>
+        <v>1204442148</v>
       </c>
       <c r="C3">
-        <v>65099355</v>
+        <v>78052402</v>
       </c>
       <c r="D3">
-        <v>273.5</v>
+        <v>327.9</v>
       </c>
       <c r="E3">
-        <v>58904630</v>
+        <v>48985614</v>
       </c>
       <c r="F3">
-        <v>288417535</v>
+        <v>239850590</v>
       </c>
       <c r="G3">
         <v>20101488</v>
@@ -499,10 +499,10 @@
         <v>238683306</v>
       </c>
       <c r="I3">
-        <v>13286295</v>
+        <v>8303935</v>
       </c>
       <c r="J3">
-        <v>27171261</v>
+        <v>16982038</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -519,19 +519,19 @@
         <v>44651</v>
       </c>
       <c r="B4">
-        <v>1207163087</v>
+        <v>1122018838</v>
       </c>
       <c r="C4">
-        <v>61839545</v>
+        <v>73200358</v>
       </c>
       <c r="D4">
-        <v>249.5</v>
+        <v>295.3</v>
       </c>
       <c r="E4">
-        <v>27252548</v>
+        <v>22135649</v>
       </c>
       <c r="F4">
-        <v>129907680</v>
+        <v>105516401</v>
       </c>
       <c r="G4">
         <v>9897433</v>
@@ -540,10 +540,10 @@
         <v>123106141</v>
       </c>
       <c r="I4">
-        <v>765532</v>
+        <v>478457</v>
       </c>
       <c r="J4">
-        <v>1460720</v>
+        <v>912950</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -560,19 +560,19 @@
         <v>44681</v>
       </c>
       <c r="B5">
-        <v>1127559751</v>
+        <v>1044792638</v>
       </c>
       <c r="C5">
-        <v>99281908</v>
+        <v>114648538</v>
       </c>
       <c r="D5">
-        <v>392.8</v>
+        <v>453.6</v>
       </c>
       <c r="E5">
-        <v>587969</v>
+        <v>486417</v>
       </c>
       <c r="F5">
-        <v>3003882</v>
+        <v>2485060</v>
       </c>
       <c r="G5">
         <v>163642</v>
@@ -581,10 +581,10 @@
         <v>1921548</v>
       </c>
       <c r="I5">
-        <v>17769101</v>
+        <v>11105688</v>
       </c>
       <c r="J5">
-        <v>34948095</v>
+        <v>21842559</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -601,19 +601,19 @@
         <v>44712</v>
       </c>
       <c r="B6">
-        <v>1133208345</v>
+        <v>1015923838</v>
       </c>
       <c r="C6">
-        <v>1370576</v>
+        <v>1662296</v>
       </c>
       <c r="D6">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="E6">
-        <v>31067820</v>
+        <v>25714401</v>
       </c>
       <c r="F6">
-        <v>154370180</v>
+        <v>127770044</v>
       </c>
       <c r="G6">
         <v>9237251</v>
@@ -622,10 +622,10 @@
         <v>118665054</v>
       </c>
       <c r="I6">
-        <v>22431326</v>
+        <v>14019579</v>
       </c>
       <c r="J6">
-        <v>43402490</v>
+        <v>27126556</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -642,19 +642,19 @@
         <v>44742</v>
       </c>
       <c r="B7">
-        <v>1060858657</v>
+        <v>991569226</v>
       </c>
       <c r="C7">
-        <v>90252492</v>
+        <v>104560318</v>
       </c>
       <c r="D7">
-        <v>348.8</v>
+        <v>404.1</v>
       </c>
       <c r="E7">
-        <v>25175756</v>
+        <v>20643362</v>
       </c>
       <c r="F7">
-        <v>124866448</v>
+        <v>102386729</v>
       </c>
       <c r="G7">
         <v>15442860</v>
@@ -663,10 +663,10 @@
         <v>182793485</v>
       </c>
       <c r="I7">
-        <v>443458</v>
+        <v>277161</v>
       </c>
       <c r="J7">
-        <v>872993</v>
+        <v>545621</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -683,19 +683,19 @@
         <v>44773</v>
       </c>
       <c r="B8">
-        <v>1155910896</v>
+        <v>1043053555</v>
       </c>
       <c r="C8">
-        <v>54123807</v>
+        <v>65637206</v>
       </c>
       <c r="D8">
-        <v>210.8</v>
+        <v>255.7</v>
       </c>
       <c r="E8">
-        <v>21415438</v>
+        <v>17721243</v>
       </c>
       <c r="F8">
-        <v>110140880</v>
+        <v>91141414</v>
       </c>
       <c r="G8">
         <v>436526</v>
@@ -704,10 +704,10 @@
         <v>5424469</v>
       </c>
       <c r="I8">
-        <v>34293594</v>
+        <v>21433496</v>
       </c>
       <c r="J8">
-        <v>67254846</v>
+        <v>42034279</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -724,19 +724,19 @@
         <v>44804</v>
       </c>
       <c r="B9">
-        <v>1183573874</v>
+        <v>1072825436</v>
       </c>
       <c r="C9">
-        <v>57960127</v>
+        <v>68972938</v>
       </c>
       <c r="D9">
-        <v>230.3</v>
+        <v>274</v>
       </c>
       <c r="E9">
-        <v>10815935</v>
+        <v>9005786</v>
       </c>
       <c r="F9">
-        <v>51490508</v>
+        <v>42873081</v>
       </c>
       <c r="G9">
         <v>22656258</v>
@@ -745,10 +745,10 @@
         <v>268940187</v>
       </c>
       <c r="I9">
-        <v>28703444</v>
+        <v>17939653</v>
       </c>
       <c r="J9">
-        <v>54044571</v>
+        <v>33777857</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -765,19 +765,19 @@
         <v>44834</v>
       </c>
       <c r="B10">
-        <v>1300451786</v>
+        <v>1167944287</v>
       </c>
       <c r="C10">
-        <v>2447554</v>
+        <v>2854140</v>
       </c>
       <c r="D10">
-        <v>8.9</v>
+        <v>10.4</v>
       </c>
       <c r="E10">
-        <v>51259554</v>
+        <v>42103387</v>
       </c>
       <c r="F10">
-        <v>238802287</v>
+        <v>196146556</v>
       </c>
       <c r="G10">
         <v>49436314</v>
@@ -786,10 +786,10 @@
         <v>579014362</v>
       </c>
       <c r="I10">
-        <v>12671782</v>
+        <v>7919864</v>
       </c>
       <c r="J10">
-        <v>23844309</v>
+        <v>14902693</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -806,19 +806,19 @@
         <v>44865</v>
       </c>
       <c r="B11">
-        <v>1369137778</v>
+        <v>1257860418</v>
       </c>
       <c r="C11">
-        <v>104171085</v>
+        <v>121806389</v>
       </c>
       <c r="D11">
-        <v>409.5</v>
+        <v>478.9</v>
       </c>
       <c r="E11">
-        <v>41558599</v>
+        <v>33647033</v>
       </c>
       <c r="F11">
-        <v>197055778</v>
+        <v>159542009</v>
       </c>
       <c r="G11">
         <v>11879836</v>
@@ -827,10 +827,10 @@
         <v>146343821</v>
       </c>
       <c r="I11">
-        <v>10794349</v>
+        <v>6746468</v>
       </c>
       <c r="J11">
-        <v>20557861</v>
+        <v>12848663</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -847,19 +847,19 @@
         <v>44895</v>
       </c>
       <c r="B12">
-        <v>1449000966</v>
+        <v>1352190583</v>
       </c>
       <c r="C12">
-        <v>80388978</v>
+        <v>92867143</v>
       </c>
       <c r="D12">
-        <v>308.3</v>
+        <v>356.2</v>
       </c>
       <c r="E12">
-        <v>31195108</v>
+        <v>25701610</v>
       </c>
       <c r="F12">
-        <v>146772553</v>
+        <v>120925723</v>
       </c>
       <c r="G12">
         <v>8380519</v>
@@ -868,10 +868,10 @@
         <v>97593368</v>
       </c>
       <c r="I12">
-        <v>132313</v>
+        <v>82696</v>
       </c>
       <c r="J12">
-        <v>252092</v>
+        <v>157558</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -888,19 +888,19 @@
         <v>44926</v>
       </c>
       <c r="B13">
-        <v>1402413908</v>
+        <v>1292670520</v>
       </c>
       <c r="C13">
-        <v>2717004</v>
+        <v>3214859</v>
       </c>
       <c r="D13">
-        <v>10.2</v>
+        <v>12.1</v>
       </c>
       <c r="E13">
-        <v>32012421</v>
+        <v>25881993</v>
       </c>
       <c r="F13">
-        <v>153218422</v>
+        <v>123876861</v>
       </c>
       <c r="G13">
         <v>25278597</v>
@@ -909,10 +909,10 @@
         <v>306459650</v>
       </c>
       <c r="I13">
-        <v>466032</v>
+        <v>291270</v>
       </c>
       <c r="J13">
-        <v>851317</v>
+        <v>532073</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -929,19 +929,19 @@
         <v>44957</v>
       </c>
       <c r="B14">
-        <v>1220067986</v>
+        <v>1104229493</v>
       </c>
       <c r="C14">
-        <v>2170886</v>
+        <v>2508914</v>
       </c>
       <c r="D14">
-        <v>8.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E14">
-        <v>26083900</v>
+        <v>21608291</v>
       </c>
       <c r="F14">
-        <v>127849489</v>
+        <v>105912422</v>
       </c>
       <c r="G14">
         <v>12760502</v>
@@ -950,10 +950,10 @@
         <v>147444673</v>
       </c>
       <c r="I14">
-        <v>9144832</v>
+        <v>5715520</v>
       </c>
       <c r="J14">
-        <v>18348365</v>
+        <v>11467728</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -970,19 +970,19 @@
         <v>44985</v>
       </c>
       <c r="B15">
-        <v>1371476880</v>
+        <v>1202006546</v>
       </c>
       <c r="C15">
-        <v>3938555</v>
+        <v>4553479</v>
       </c>
       <c r="D15">
-        <v>15</v>
+        <v>17.4</v>
       </c>
       <c r="E15">
-        <v>57716770</v>
+        <v>47895212</v>
       </c>
       <c r="F15">
-        <v>278025224</v>
+        <v>230714173</v>
       </c>
       <c r="G15">
         <v>15213796</v>
@@ -991,10 +991,10 @@
         <v>176629869</v>
       </c>
       <c r="I15">
-        <v>33571888</v>
+        <v>20982430</v>
       </c>
       <c r="J15">
-        <v>61046992</v>
+        <v>38154370</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -1011,19 +1011,19 @@
         <v>45016</v>
       </c>
       <c r="B16">
-        <v>1305292346</v>
+        <v>1178687075</v>
       </c>
       <c r="C16">
-        <v>138667327</v>
+        <v>161453766</v>
       </c>
       <c r="D16">
-        <v>513.6</v>
+        <v>598</v>
       </c>
       <c r="E16">
-        <v>11200998</v>
+        <v>8997833</v>
       </c>
       <c r="F16">
-        <v>53168592</v>
+        <v>42710672</v>
       </c>
       <c r="G16">
         <v>8004415</v>
@@ -1032,10 +1032,10 @@
         <v>93004858</v>
       </c>
       <c r="I16">
-        <v>33651678</v>
+        <v>21032299</v>
       </c>
       <c r="J16">
-        <v>64388518</v>
+        <v>40242824</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -1052,19 +1052,19 @@
         <v>45046</v>
       </c>
       <c r="B17">
-        <v>1032964955</v>
+        <v>931990505</v>
       </c>
       <c r="C17">
-        <v>1079837</v>
+        <v>1343505</v>
       </c>
       <c r="D17">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="E17">
-        <v>1510516</v>
+        <v>1255563</v>
       </c>
       <c r="F17">
-        <v>7041335</v>
+        <v>5852863</v>
       </c>
       <c r="G17">
         <v>10210174</v>
@@ -1073,10 +1073,10 @@
         <v>120215903</v>
       </c>
       <c r="I17">
-        <v>13786092</v>
+        <v>8616307</v>
       </c>
       <c r="J17">
-        <v>25493828</v>
+        <v>15933643</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -1093,19 +1093,19 @@
         <v>45077</v>
       </c>
       <c r="B18">
-        <v>1156056699</v>
+        <v>1045169843</v>
       </c>
       <c r="C18">
-        <v>46108036</v>
+        <v>53523045</v>
       </c>
       <c r="D18">
-        <v>173.6</v>
+        <v>201.5</v>
       </c>
       <c r="E18">
-        <v>51242796</v>
+        <v>42475823</v>
       </c>
       <c r="F18">
-        <v>240475521</v>
+        <v>199333301</v>
       </c>
       <c r="G18">
         <v>6398596</v>
@@ -1114,10 +1114,10 @@
         <v>75227077</v>
       </c>
       <c r="I18">
-        <v>11746517</v>
+        <v>7341573</v>
       </c>
       <c r="J18">
-        <v>22131591</v>
+        <v>13832244</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -1134,19 +1134,19 @@
         <v>45107</v>
       </c>
       <c r="B19">
-        <v>1242671696</v>
+        <v>1139632204</v>
       </c>
       <c r="C19">
-        <v>184411012</v>
+        <v>213363359</v>
       </c>
       <c r="D19">
-        <v>705.1</v>
+        <v>815.8</v>
       </c>
       <c r="E19">
-        <v>21511434</v>
+        <v>17716199</v>
       </c>
       <c r="F19">
-        <v>101376627</v>
+        <v>83490878</v>
       </c>
       <c r="G19">
         <v>15428563</v>
@@ -1155,10 +1155,10 @@
         <v>182701407</v>
       </c>
       <c r="I19">
-        <v>30129055</v>
+        <v>18830659</v>
       </c>
       <c r="J19">
-        <v>57176188</v>
+        <v>35735117</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -1175,19 +1175,19 @@
         <v>45138</v>
       </c>
       <c r="B20">
-        <v>1294969128</v>
+        <v>1168682192</v>
       </c>
       <c r="C20">
-        <v>99834368</v>
+        <v>117291394</v>
       </c>
       <c r="D20">
-        <v>354.7</v>
+        <v>416.7</v>
       </c>
       <c r="E20">
-        <v>24502160</v>
+        <v>19615747</v>
       </c>
       <c r="F20">
-        <v>120617802</v>
+        <v>96563255</v>
       </c>
       <c r="G20">
         <v>5040150</v>
@@ -1196,10 +1196,10 @@
         <v>64123932</v>
       </c>
       <c r="I20">
-        <v>68566422</v>
+        <v>42854014</v>
       </c>
       <c r="J20">
-        <v>130707430</v>
+        <v>81692144</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -1216,19 +1216,19 @@
         <v>45169</v>
       </c>
       <c r="B21">
-        <v>1358739493</v>
+        <v>1224168784</v>
       </c>
       <c r="C21">
-        <v>41475034</v>
+        <v>50073643</v>
       </c>
       <c r="D21">
-        <v>152.9</v>
+        <v>184.6</v>
       </c>
       <c r="E21">
-        <v>44748328</v>
+        <v>36387724</v>
       </c>
       <c r="F21">
-        <v>215705557</v>
+        <v>175403967</v>
       </c>
       <c r="G21">
         <v>131326</v>
@@ -1237,10 +1237,10 @@
         <v>1502363</v>
       </c>
       <c r="I21">
-        <v>21956418</v>
+        <v>13722761</v>
       </c>
       <c r="J21">
-        <v>46416473</v>
+        <v>29010295</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -1257,19 +1257,19 @@
         <v>45199</v>
       </c>
       <c r="B22">
-        <v>1341338774</v>
+        <v>1226690068</v>
       </c>
       <c r="C22">
-        <v>65003723</v>
+        <v>78644039</v>
       </c>
       <c r="D22">
-        <v>244.5</v>
+        <v>295.8</v>
       </c>
       <c r="E22">
-        <v>41584998</v>
+        <v>34258932</v>
       </c>
       <c r="F22">
-        <v>190441066</v>
+        <v>156890894</v>
       </c>
       <c r="G22">
         <v>15765665</v>
@@ -1278,10 +1278,10 @@
         <v>181597414</v>
       </c>
       <c r="I22">
-        <v>11985391</v>
+        <v>7490870</v>
       </c>
       <c r="J22">
-        <v>22837310</v>
+        <v>14273319</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1298,19 +1298,19 @@
         <v>45230</v>
       </c>
       <c r="B23">
-        <v>1542589559</v>
+        <v>1408017755</v>
       </c>
       <c r="C23">
-        <v>172966046</v>
+        <v>200462205</v>
       </c>
       <c r="D23">
-        <v>621.1</v>
+        <v>719.9</v>
       </c>
       <c r="E23">
-        <v>57690788</v>
+        <v>47938359</v>
       </c>
       <c r="F23">
-        <v>257253226</v>
+        <v>213765453</v>
       </c>
       <c r="G23">
         <v>217215</v>
@@ -1319,10 +1319,10 @@
         <v>2470756</v>
       </c>
       <c r="I23">
-        <v>31145099</v>
+        <v>19465687</v>
       </c>
       <c r="J23">
-        <v>58569780</v>
+        <v>36606112</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1339,19 +1339,19 @@
         <v>45260</v>
       </c>
       <c r="B24">
-        <v>1607660070</v>
+        <v>1450925188</v>
       </c>
       <c r="C24">
-        <v>42529464</v>
+        <v>52192607</v>
       </c>
       <c r="D24">
-        <v>160.5</v>
+        <v>197</v>
       </c>
       <c r="E24">
-        <v>22725491</v>
+        <v>18275408</v>
       </c>
       <c r="F24">
-        <v>108967853</v>
+        <v>87629876</v>
       </c>
       <c r="G24">
         <v>290113</v>
@@ -1360,10 +1360,10 @@
         <v>3402184</v>
       </c>
       <c r="I24">
-        <v>49553702</v>
+        <v>30971063</v>
       </c>
       <c r="J24">
-        <v>94332184</v>
+        <v>58957615</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -1380,19 +1380,19 @@
         <v>45291</v>
       </c>
       <c r="B25">
-        <v>1660388291</v>
+        <v>1517646672</v>
       </c>
       <c r="C25">
-        <v>177372563</v>
+        <v>208132879</v>
       </c>
       <c r="D25">
-        <v>638.1</v>
+        <v>748.7</v>
       </c>
       <c r="E25">
-        <v>55247187</v>
+        <v>45806265</v>
       </c>
       <c r="F25">
-        <v>248919415</v>
+        <v>206382795</v>
       </c>
       <c r="G25">
         <v>23047478</v>
@@ -1401,10 +1401,10 @@
         <v>259511335</v>
       </c>
       <c r="I25">
-        <v>23888866</v>
+        <v>14930541</v>
       </c>
       <c r="J25">
-        <v>46094894</v>
+        <v>28809309</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -1421,19 +1421,19 @@
         <v>45322</v>
       </c>
       <c r="B26">
-        <v>1532555218</v>
+        <v>1399581322</v>
       </c>
       <c r="C26">
-        <v>56487063</v>
+        <v>68145447</v>
       </c>
       <c r="D26">
-        <v>215.4</v>
+        <v>259.8</v>
       </c>
       <c r="E26">
-        <v>33677224</v>
+        <v>26997878</v>
       </c>
       <c r="F26">
-        <v>149442031</v>
+        <v>119802564</v>
       </c>
       <c r="G26">
         <v>136575</v>
@@ -1442,10 +1442,10 @@
         <v>1567338</v>
       </c>
       <c r="I26">
-        <v>23612986</v>
+        <v>14758116</v>
       </c>
       <c r="J26">
-        <v>42199834</v>
+        <v>26374896</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -1462,19 +1462,19 @@
         <v>45351</v>
       </c>
       <c r="B27">
-        <v>1291467574</v>
+        <v>1160007387</v>
       </c>
       <c r="C27">
-        <v>1307906</v>
+        <v>1561492</v>
       </c>
       <c r="D27">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="E27">
-        <v>1331676</v>
+        <v>1099661</v>
       </c>
       <c r="F27">
-        <v>6023812</v>
+        <v>4974295</v>
       </c>
       <c r="G27">
         <v>28289892</v>
@@ -1483,10 +1483,10 @@
         <v>304679830</v>
       </c>
       <c r="I27">
-        <v>39947814</v>
+        <v>24967384</v>
       </c>
       <c r="J27">
-        <v>74529297</v>
+        <v>46580811</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -1503,19 +1503,19 @@
         <v>45382</v>
       </c>
       <c r="B28">
-        <v>1240218920</v>
+        <v>1092689382</v>
       </c>
       <c r="C28">
-        <v>2542369</v>
+        <v>2935249</v>
       </c>
       <c r="D28">
-        <v>9.199999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="E28">
-        <v>8218627</v>
+        <v>6723885</v>
       </c>
       <c r="F28">
-        <v>36879834</v>
+        <v>30172404</v>
       </c>
       <c r="G28">
         <v>453319</v>
@@ -1524,10 +1524,10 @@
         <v>5314428</v>
       </c>
       <c r="I28">
-        <v>49297535</v>
+        <v>30810959</v>
       </c>
       <c r="J28">
-        <v>88547581</v>
+        <v>55342238</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -1544,19 +1544,19 @@
         <v>45412</v>
       </c>
       <c r="B29">
-        <v>1164255397</v>
+        <v>1008678988</v>
       </c>
       <c r="C29">
-        <v>1106503</v>
+        <v>1324172</v>
       </c>
       <c r="D29">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="E29">
-        <v>80677224</v>
+        <v>66999225</v>
       </c>
       <c r="F29">
-        <v>365806142</v>
+        <v>303787448</v>
       </c>
       <c r="G29">
         <v>9360319</v>
@@ -1565,10 +1565,10 @@
         <v>101022863</v>
       </c>
       <c r="I29">
-        <v>30265508</v>
+        <v>18915942</v>
       </c>
       <c r="J29">
-        <v>52455464</v>
+        <v>32784665</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         <v>45443</v>
       </c>
       <c r="B30">
-        <v>1155806737</v>
+        <v>1058984279</v>
       </c>
       <c r="C30">
-        <v>121597852</v>
+        <v>141763283</v>
       </c>
       <c r="D30">
-        <v>429.2</v>
+        <v>500.4</v>
       </c>
       <c r="E30">
-        <v>26981886</v>
+        <v>21904042</v>
       </c>
       <c r="F30">
-        <v>120592660</v>
+        <v>97897780</v>
       </c>
       <c r="G30">
         <v>30423830</v>
@@ -1606,10 +1606,10 @@
         <v>347493944</v>
       </c>
       <c r="I30">
-        <v>7026746</v>
+        <v>4391716</v>
       </c>
       <c r="J30">
-        <v>12988818</v>
+        <v>8118011</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -1626,19 +1626,19 @@
         <v>45473</v>
       </c>
       <c r="B31">
-        <v>1262526257</v>
+        <v>1151831874</v>
       </c>
       <c r="C31">
-        <v>131634909</v>
+        <v>152966252</v>
       </c>
       <c r="D31">
-        <v>466.6</v>
+        <v>542.2</v>
       </c>
       <c r="E31">
-        <v>93836281</v>
+        <v>78023172</v>
       </c>
       <c r="F31">
-        <v>430567985</v>
+        <v>358009502</v>
       </c>
       <c r="G31">
         <v>18302632</v>
@@ -1647,10 +1647,10 @@
         <v>205260318</v>
       </c>
       <c r="I31">
-        <v>24110765</v>
+        <v>15069228</v>
       </c>
       <c r="J31">
-        <v>44082243</v>
+        <v>27551402</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -1667,19 +1667,19 @@
         <v>45504</v>
       </c>
       <c r="B32">
-        <v>1369289381</v>
+        <v>1234420859</v>
       </c>
       <c r="C32">
-        <v>93664884</v>
+        <v>111963409</v>
       </c>
       <c r="D32">
-        <v>335.1</v>
+        <v>400.6</v>
       </c>
       <c r="E32">
-        <v>61710982</v>
+        <v>51227635</v>
       </c>
       <c r="F32">
-        <v>291853004</v>
+        <v>242273556</v>
       </c>
       <c r="G32">
         <v>18310373</v>
@@ -1688,10 +1688,10 @@
         <v>208381213</v>
       </c>
       <c r="I32">
-        <v>53579632</v>
+        <v>33487270</v>
       </c>
       <c r="J32">
-        <v>93880993</v>
+        <v>58675621</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -1708,19 +1708,19 @@
         <v>45535</v>
       </c>
       <c r="B33">
-        <v>1255004622</v>
+        <v>1172674444</v>
       </c>
       <c r="C33">
-        <v>80769037</v>
+        <v>98179431</v>
       </c>
       <c r="D33">
-        <v>289.7</v>
+        <v>352.2</v>
       </c>
       <c r="E33">
-        <v>1826817</v>
+        <v>1521848</v>
       </c>
       <c r="F33">
-        <v>7916973</v>
+        <v>6595313</v>
       </c>
       <c r="G33">
         <v>20529881</v>
@@ -1729,10 +1729,10 @@
         <v>237875080</v>
       </c>
       <c r="I33">
-        <v>594493</v>
+        <v>371558</v>
       </c>
       <c r="J33">
-        <v>1083283</v>
+        <v>677052</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -1749,19 +1749,19 @@
         <v>45565</v>
       </c>
       <c r="B34">
-        <v>1155578552</v>
+        <v>1104639774</v>
       </c>
       <c r="C34">
-        <v>110518332</v>
+        <v>128405652</v>
       </c>
       <c r="D34">
-        <v>404.7</v>
+        <v>470.2</v>
       </c>
       <c r="E34">
-        <v>777481</v>
+        <v>642291</v>
       </c>
       <c r="F34">
-        <v>3388207</v>
+        <v>2799057</v>
       </c>
       <c r="G34">
         <v>21931262</v>
@@ -1770,10 +1770,10 @@
         <v>256681047</v>
       </c>
       <c r="I34">
-        <v>300300</v>
+        <v>187687</v>
       </c>
       <c r="J34">
-        <v>535381</v>
+        <v>334613</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -1790,19 +1790,19 @@
         <v>45596</v>
       </c>
       <c r="B35">
-        <v>1385770096</v>
+        <v>1278886812</v>
       </c>
       <c r="C35">
-        <v>120712865</v>
+        <v>142422601</v>
       </c>
       <c r="D35">
-        <v>413.6</v>
+        <v>488</v>
       </c>
       <c r="E35">
-        <v>16577940</v>
+        <v>13516015</v>
       </c>
       <c r="F35">
-        <v>73775858</v>
+        <v>60149545</v>
       </c>
       <c r="G35">
         <v>7762434</v>
@@ -1811,10 +1811,10 @@
         <v>83152003</v>
       </c>
       <c r="I35">
-        <v>29046870</v>
+        <v>18154294</v>
       </c>
       <c r="J35">
-        <v>54494950</v>
+        <v>34059344</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -1831,19 +1831,19 @@
         <v>45626</v>
       </c>
       <c r="B36">
-        <v>1554515204</v>
+        <v>1389378393</v>
       </c>
       <c r="C36">
-        <v>1404555</v>
+        <v>1679009</v>
       </c>
       <c r="D36">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="E36">
-        <v>63905106</v>
+        <v>53033831</v>
       </c>
       <c r="F36">
-        <v>268652032</v>
+        <v>222950047</v>
       </c>
       <c r="G36">
         <v>7179108</v>
@@ -1852,10 +1852,10 @@
         <v>82537333</v>
       </c>
       <c r="I36">
-        <v>56669126</v>
+        <v>35418204</v>
       </c>
       <c r="J36">
-        <v>95343363</v>
+        <v>59589602</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -1872,19 +1872,19 @@
         <v>45657</v>
       </c>
       <c r="B37">
-        <v>1535419911</v>
+        <v>1415606429</v>
       </c>
       <c r="C37">
-        <v>108979261</v>
+        <v>131341765</v>
       </c>
       <c r="D37">
-        <v>385.9</v>
+        <v>465.1</v>
       </c>
       <c r="E37">
-        <v>63379711</v>
+        <v>52343055</v>
       </c>
       <c r="F37">
-        <v>277953453</v>
+        <v>229551897</v>
       </c>
       <c r="G37">
         <v>258120</v>
@@ -1893,10 +1893,10 @@
         <v>2845040</v>
       </c>
       <c r="I37">
-        <v>852193</v>
+        <v>532621</v>
       </c>
       <c r="J37">
-        <v>1497542</v>
+        <v>935964</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -1913,19 +1913,19 @@
         <v>45688</v>
       </c>
       <c r="B38">
-        <v>1556936403</v>
+        <v>1420413849</v>
       </c>
       <c r="C38">
-        <v>113898972</v>
+        <v>131477716</v>
       </c>
       <c r="D38">
-        <v>373.5</v>
+        <v>431.1</v>
       </c>
       <c r="E38">
-        <v>30885577</v>
+        <v>24772751</v>
       </c>
       <c r="F38">
-        <v>131419413</v>
+        <v>105409083</v>
       </c>
       <c r="G38">
         <v>15032446</v>
@@ -1934,10 +1934,10 @@
         <v>156707370</v>
       </c>
       <c r="I38">
-        <v>28212132</v>
+        <v>17632583</v>
       </c>
       <c r="J38">
-        <v>51095694</v>
+        <v>31934809</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -1954,19 +1954,19 @@
         <v>45716</v>
       </c>
       <c r="B39">
-        <v>1349496494</v>
+        <v>1224733251</v>
       </c>
       <c r="C39">
-        <v>1879109</v>
+        <v>2194242</v>
       </c>
       <c r="D39">
-        <v>6.8</v>
+        <v>7.9</v>
       </c>
       <c r="E39">
-        <v>38285795</v>
+        <v>31137184</v>
       </c>
       <c r="F39">
-        <v>173801869</v>
+        <v>141350096</v>
       </c>
       <c r="G39">
         <v>406469</v>
@@ -1975,10 +1975,10 @@
         <v>4218439</v>
       </c>
       <c r="I39">
-        <v>12006527</v>
+        <v>7504080</v>
       </c>
       <c r="J39">
-        <v>20282897</v>
+        <v>12676811</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -1995,19 +1995,19 @@
         <v>45747</v>
       </c>
       <c r="B40">
-        <v>1186893777</v>
+        <v>1063482066</v>
       </c>
       <c r="C40">
-        <v>2220167</v>
+        <v>2608501</v>
       </c>
       <c r="D40">
-        <v>8.1</v>
+        <v>9.5</v>
       </c>
       <c r="E40">
-        <v>36333378</v>
+        <v>29655382</v>
       </c>
       <c r="F40">
-        <v>159122701</v>
+        <v>129876294</v>
       </c>
       <c r="G40">
         <v>24052906</v>
@@ -2016,10 +2016,10 @@
         <v>256443048</v>
       </c>
       <c r="I40">
-        <v>14102888</v>
+        <v>8814305</v>
       </c>
       <c r="J40">
-        <v>24655197</v>
+        <v>15409498</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -2036,19 +2036,19 @@
         <v>45777</v>
       </c>
       <c r="B41">
-        <v>1184586761</v>
+        <v>1067985388</v>
       </c>
       <c r="C41">
-        <v>46593002</v>
+        <v>56918419</v>
       </c>
       <c r="D41">
-        <v>164.4</v>
+        <v>200.9</v>
       </c>
       <c r="E41">
-        <v>71825399</v>
+        <v>59544298</v>
       </c>
       <c r="F41">
-        <v>298576977</v>
+        <v>247524647</v>
       </c>
       <c r="G41">
         <v>11463816</v>
@@ -2057,10 +2057,10 @@
         <v>129068782</v>
       </c>
       <c r="I41">
-        <v>14003649</v>
+        <v>8752281</v>
       </c>
       <c r="J41">
-        <v>24139790</v>
+        <v>15087369</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -2077,19 +2077,19 @@
         <v>45808</v>
       </c>
       <c r="B42">
-        <v>1178252286</v>
+        <v>1092287115</v>
       </c>
       <c r="C42">
-        <v>163000956</v>
+        <v>188527512</v>
       </c>
       <c r="D42">
-        <v>551.5</v>
+        <v>637.9</v>
       </c>
       <c r="E42">
-        <v>47379219</v>
+        <v>39422134</v>
       </c>
       <c r="F42">
-        <v>194107044</v>
+        <v>161507810</v>
       </c>
       <c r="G42">
         <v>94004</v>
@@ -2098,10 +2098,10 @@
         <v>1007655</v>
       </c>
       <c r="I42">
-        <v>11543375</v>
+        <v>7214610</v>
       </c>
       <c r="J42">
-        <v>20182628</v>
+        <v>12614142</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -2118,19 +2118,19 @@
         <v>45838</v>
       </c>
       <c r="B43">
-        <v>1095321043</v>
+        <v>1027186575</v>
       </c>
       <c r="C43">
-        <v>50982826</v>
+        <v>60696686</v>
       </c>
       <c r="D43">
-        <v>177.8</v>
+        <v>211.6</v>
       </c>
       <c r="E43">
-        <v>30516376</v>
+        <v>24795023</v>
       </c>
       <c r="F43">
-        <v>125679729</v>
+        <v>102116705</v>
       </c>
       <c r="G43">
         <v>254070</v>
@@ -2139,10 +2139,10 @@
         <v>2752624</v>
       </c>
       <c r="I43">
-        <v>609354</v>
+        <v>380846</v>
       </c>
       <c r="J43">
-        <v>1039134</v>
+        <v>649459</v>
       </c>
       <c r="K43">
         <v>1</v>
@@ -2159,19 +2159,19 @@
         <v>45869</v>
       </c>
       <c r="B44">
-        <v>987664863</v>
+        <v>940448864</v>
       </c>
       <c r="C44">
-        <v>108829980</v>
+        <v>126360978</v>
       </c>
       <c r="D44">
-        <v>366.5</v>
+        <v>425.6</v>
       </c>
       <c r="E44">
-        <v>19814301</v>
+        <v>16321425</v>
       </c>
       <c r="F44">
-        <v>82330574</v>
+        <v>67817294</v>
       </c>
       <c r="G44">
         <v>6651018</v>
@@ -2180,10 +2180,10 @@
         <v>73725482</v>
       </c>
       <c r="I44">
-        <v>269178</v>
+        <v>168237</v>
       </c>
       <c r="J44">
-        <v>458292</v>
+        <v>286432</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -2200,19 +2200,19 @@
         <v>45900</v>
       </c>
       <c r="B45">
-        <v>1202337143</v>
+        <v>1080142959</v>
       </c>
       <c r="C45">
-        <v>3209427</v>
+        <v>3712804</v>
       </c>
       <c r="D45">
-        <v>11.1</v>
+        <v>12.8</v>
       </c>
       <c r="E45">
-        <v>53785071</v>
+        <v>44528578</v>
       </c>
       <c r="F45">
-        <v>220391316</v>
+        <v>182461636</v>
       </c>
       <c r="G45">
         <v>15564430</v>
@@ -2221,10 +2221,10 @@
         <v>161361130</v>
       </c>
       <c r="I45">
-        <v>27443776</v>
+        <v>17152360</v>
       </c>
       <c r="J45">
-        <v>48167914</v>
+        <v>30104946</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -2241,19 +2241,19 @@
         <v>45930</v>
       </c>
       <c r="B46">
-        <v>1342506005</v>
+        <v>1227542978</v>
       </c>
       <c r="C46">
-        <v>93076552</v>
+        <v>112253626</v>
       </c>
       <c r="D46">
-        <v>323.9</v>
+        <v>390.7</v>
       </c>
       <c r="E46">
-        <v>54988367</v>
+        <v>45714212</v>
       </c>
       <c r="F46">
-        <v>236324488</v>
+        <v>196466787</v>
       </c>
       <c r="G46">
         <v>11865574</v>
@@ -2262,10 +2262,10 @@
         <v>124056668</v>
       </c>
       <c r="I46">
-        <v>15826712</v>
+        <v>9891695</v>
       </c>
       <c r="J46">
-        <v>26732153</v>
+        <v>16707596</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -2282,19 +2282,19 @@
         <v>45961</v>
       </c>
       <c r="B47">
-        <v>1522970387</v>
+        <v>1392559133</v>
       </c>
       <c r="C47">
-        <v>111230285</v>
+        <v>128416330</v>
       </c>
       <c r="D47">
-        <v>364</v>
+        <v>420.3</v>
       </c>
       <c r="E47">
-        <v>63706414</v>
+        <v>52993263</v>
       </c>
       <c r="F47">
-        <v>278794541</v>
+        <v>231911222</v>
       </c>
       <c r="G47">
         <v>13385970</v>
@@ -2303,10 +2303,10 @@
         <v>139138476</v>
       </c>
       <c r="I47">
-        <v>20751809</v>
+        <v>12969881</v>
       </c>
       <c r="J47">
-        <v>33398773</v>
+        <v>20874233</v>
       </c>
       <c r="K47">
         <v>1</v>
@@ -2323,19 +2323,19 @@
         <v>45991</v>
       </c>
       <c r="B48">
-        <v>1696322474</v>
+        <v>1539435253</v>
       </c>
       <c r="C48">
-        <v>277692073</v>
+        <v>321351876</v>
       </c>
       <c r="D48">
-        <v>945.9</v>
+        <v>1094.6</v>
       </c>
       <c r="E48">
-        <v>58968408</v>
+        <v>48600842</v>
       </c>
       <c r="F48">
-        <v>265252546</v>
+        <v>218617011</v>
       </c>
       <c r="G48">
         <v>11575280</v>
@@ -2344,10 +2344,10 @@
         <v>121409526</v>
       </c>
       <c r="I48">
-        <v>88565249</v>
+        <v>55353280</v>
       </c>
       <c r="J48">
-        <v>147951228</v>
+        <v>92469518</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -2364,19 +2364,19 @@
         <v>46022</v>
       </c>
       <c r="B49">
-        <v>1705794702</v>
+        <v>1559883523</v>
       </c>
       <c r="C49">
-        <v>166407528</v>
+        <v>195061877</v>
       </c>
       <c r="D49">
-        <v>544.8</v>
+        <v>638.7</v>
       </c>
       <c r="E49">
-        <v>32907608</v>
+        <v>26748313</v>
       </c>
       <c r="F49">
-        <v>136721111</v>
+        <v>111131115</v>
       </c>
       <c r="G49">
         <v>12323991</v>
@@ -2385,10 +2385,10 @@
         <v>133847604</v>
       </c>
       <c r="I49">
-        <v>28637509</v>
+        <v>17898443</v>
       </c>
       <c r="J49">
-        <v>48558848</v>
+        <v>30349280</v>
       </c>
       <c r="K49">
         <v>1</v>
